--- a/data/trans_orig/IP07C09-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07C09-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido hablar de todos sus amigos en 2007 (tasa de respuesta: 89,49%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as en 2007 (tasa de respuesta: 89,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1726</t>
+          <t>1783</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>7264</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3660</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11106</t>
+          <t>10930</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6551</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16126</t>
+          <t>15443</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>40,39%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11024</t>
+          <t>10427</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6457</t>
+          <t>6595</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14296</t>
+          <t>14638</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13367</t>
+          <t>13443</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23224</t>
+          <t>23317</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>60,99%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>657</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8890</t>
+          <t>9411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4078</t>
+          <t>4482</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12268</t>
+          <t>12360</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,33%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3586</t>
+          <t>3358</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>3253</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5233</t>
+          <t>5207</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22824</t>
+          <t>23350</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32967</t>
+          <t>33237</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37104</t>
+          <t>37228</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46686</t>
+          <t>46655</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64074</t>
+          <t>63944</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77565</t>
+          <t>77551</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,01%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8380</t>
+          <t>8832</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18621</t>
+          <t>18632</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6545</t>
+          <t>6733</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15954</t>
+          <t>15802</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17363</t>
+          <t>17320</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30219</t>
+          <t>30758</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>31,34%</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4613</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>4736</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>672</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6682</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3831</t>
+          <t>2746</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3437</t>
+          <t>3505</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8763</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17652</t>
+          <t>18149</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3088</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9896</t>
+          <t>9813</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13486</t>
+          <t>14204</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25375</t>
+          <t>25282</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>46,8%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10048</t>
+          <t>10237</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18603</t>
+          <t>19148</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13464</t>
+          <t>13570</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20429</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26254</t>
+          <t>25931</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>38466</t>
+          <t>37285</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>69,02%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>678</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>5012</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2901</t>
+          <t>2994</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>700</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6964</t>
+          <t>6487</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6284</t>
+          <t>6021</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14767</t>
+          <t>14350</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5203</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13097</t>
+          <t>12929</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13455</t>
+          <t>13374</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25391</t>
+          <t>24876</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>38,74%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>16274</t>
+          <t>16772</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25129</t>
+          <t>25493</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>15652</t>
+          <t>16102</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>24847</t>
+          <t>24479</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>35253</t>
+          <t>35595</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>47482</t>
+          <t>47425</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>73,86%</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4195</t>
+          <t>4360</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>786</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>6351</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7842</t>
+          <t>7936</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5294</t>
+          <t>5187</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12525</t>
+          <t>12121</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5826</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>13196</t>
+          <t>13492</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>13163</t>
+          <t>12722</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>23355</t>
+          <t>23309</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>55,86%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10939</t>
+          <t>11353</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8639</t>
+          <t>8343</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>16308</t>
+          <t>16009</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>14765</t>
+          <t>15089</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>25250</t>
+          <t>25158</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,29%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>726</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6465</t>
+          <t>6760</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>723</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7197</t>
+          <t>7294</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,48%</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3627</t>
+          <t>2940</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3633</t>
+          <t>4377</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>4356</t>
+          <t>4167</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>11929</t>
+          <t>11846</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>10080</t>
+          <t>10269</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>9230</t>
+          <t>9386</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>19808</t>
+          <t>19046</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>35,73%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>11506</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>19167</t>
+          <t>19304</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>14862</t>
+          <t>15026</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>22696</t>
+          <t>22513</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>28749</t>
+          <t>28822</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>39873</t>
+          <t>39548</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>74,2%</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4093</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1411</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6829</t>
+          <t>6825</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2399</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8849</t>
+          <t>8959</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,81%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>17190</t>
+          <t>16688</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>28958</t>
+          <t>28010</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>21770</t>
+          <t>21821</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>33817</t>
+          <t>32976</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>41924</t>
+          <t>41821</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>59008</t>
+          <t>58312</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>56,6%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>16908</t>
+          <t>17365</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>28278</t>
+          <t>28586</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>12686</t>
+          <t>12705</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>24273</t>
+          <t>24025</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>32690</t>
+          <t>32602</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>49138</t>
+          <t>48856</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,42%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2185</t>
+          <t>2197</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>9417</t>
+          <t>10092</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>3345</t>
+          <t>3323</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>11685</t>
+          <t>10941</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>7507</t>
+          <t>7586</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>17980</t>
+          <t>17493</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>16,98%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>23981</t>
+          <t>23386</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>37144</t>
+          <t>37046</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>23096</t>
+          <t>23456</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>36042</t>
+          <t>35755</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>50799</t>
+          <t>50243</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>68950</t>
+          <t>68921</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,61%</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5619,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>29786</t>
+          <t>29794</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>44065</t>
+          <t>44164</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>27641</t>
+          <t>27621</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>41038</t>
+          <t>40476</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>60583</t>
+          <t>61185</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>80305</t>
+          <t>80197</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>55,4%</t>
         </is>
       </c>
     </row>
@@ -5732,12 +5732,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3353</t>
+          <t>3890</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>11591</t>
+          <t>11986</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3341</t>
+          <t>2783</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>11442</t>
+          <t>10660</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>8800</t>
+          <t>8722</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>19809</t>
+          <t>19760</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,65%</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3284</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3857</t>
+          <t>2983</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>4555</t>
+          <t>4110</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>112389</t>
+          <t>112035</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>138787</t>
+          <t>138598</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>123651</t>
+          <t>122870</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>149810</t>
+          <t>149748</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>241035</t>
+          <t>240837</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>281190</t>
+          <t>280067</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>46,88%</t>
         </is>
       </c>
     </row>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>124994</t>
+          <t>125639</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>152734</t>
+          <t>153669</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>127681</t>
+          <t>129111</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>155918</t>
+          <t>156832</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>261406</t>
+          <t>264766</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>299855</t>
+          <t>303881</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,86%</t>
         </is>
       </c>
     </row>
@@ -6414,12 +6414,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>16007</t>
+          <t>16542</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>30136</t>
+          <t>31882</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>19285</t>
+          <t>19792</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>36049</t>
+          <t>35501</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6484,12 +6484,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>39665</t>
+          <t>40174</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>61561</t>
+          <t>61424</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -6527,12 +6527,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>674</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>6558</t>
+          <t>7063</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>5757</t>
+          <t>4729</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6597,12 +6597,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>1479</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>8762</t>
+          <t>8894</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido hablar de todos sus amigos en 2012 (tasa de respuesta: 95,1%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as en 2012 (tasa de respuesta: 95,1%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7106,12 +7106,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14850</t>
+          <t>15040</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20970</t>
+          <t>21016</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7121,12 +7121,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15166</t>
+          <t>15123</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23868</t>
+          <t>23909</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32543</t>
+          <t>32404</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43686</t>
+          <t>43262</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>81,3%</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3890</t>
+          <t>4217</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7254,12 +7254,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5413</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13792</t>
+          <t>14148</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7289,12 +7289,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15177</t>
+          <t>15398</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7304,12 +7304,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,94%</t>
         </is>
       </c>
     </row>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3718</t>
+          <t>4836</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5497</t>
+          <t>6043</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>732</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6519</t>
+          <t>7096</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -7450,7 +7450,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>3694</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4463</t>
+          <t>3530</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4823</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3752</t>
+          <t>4667</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -7788,12 +7788,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31331</t>
+          <t>31190</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40731</t>
+          <t>40607</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37834</t>
+          <t>37622</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47830</t>
+          <t>47744</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7838,12 +7838,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>72777</t>
+          <t>73046</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86454</t>
+          <t>86680</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7873,12 +7873,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,95%</t>
         </is>
       </c>
     </row>
@@ -7901,12 +7901,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2689</t>
+          <t>2678</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>10126</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7981</t>
+          <t>7854</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7951,12 +7951,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15203</t>
+          <t>15376</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7986,12 +7986,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7399</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9702</t>
+          <t>9547</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4071</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13948</t>
+          <t>14446</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>3321</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3668</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3996</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8245,7 +8245,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>4113</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8280,7 +8280,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4472</t>
+          <t>3432</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>654</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5430</t>
+          <t>5831</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -8470,12 +8470,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>8870</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16232</t>
+          <t>16751</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8485,12 +8485,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12838</t>
+          <t>13053</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22072</t>
+          <t>22257</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24046</t>
+          <t>24582</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35984</t>
+          <t>36006</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>67,15%</t>
         </is>
       </c>
     </row>
@@ -8583,12 +8583,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5088</t>
+          <t>5589</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13433</t>
+          <t>12908</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8598,12 +8598,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8618,12 +8618,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>6835</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15518</t>
+          <t>15534</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14138</t>
+          <t>14497</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25754</t>
+          <t>26495</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>49,41%</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4476</t>
+          <t>4819</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>713</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7011</t>
+          <t>6605</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,32%</t>
         </is>
       </c>
     </row>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3305</t>
+          <t>3299</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3629</t>
+          <t>3275</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -9152,12 +9152,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14677</t>
+          <t>14024</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24767</t>
+          <t>24888</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15453</t>
+          <t>15345</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25236</t>
+          <t>25304</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9202,12 +9202,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33368</t>
+          <t>33505</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>46963</t>
+          <t>47531</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>65,14%</t>
         </is>
       </c>
     </row>
@@ -9265,12 +9265,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9838</t>
+          <t>10211</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19878</t>
+          <t>20865</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9280,12 +9280,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9300,12 +9300,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7597</t>
+          <t>7988</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>17174</t>
+          <t>18071</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9335,12 +9335,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>20786</t>
+          <t>20724</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>34150</t>
+          <t>34119</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9350,12 +9350,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>46,76%</t>
         </is>
       </c>
     </row>
@@ -9378,12 +9378,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8371</t>
+          <t>7458</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9393,12 +9393,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9418,7 +9418,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4047</t>
+          <t>4521</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>2143</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9776</t>
+          <t>9706</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,3%</t>
         </is>
       </c>
     </row>
@@ -9531,7 +9531,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3397</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3480</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -9834,12 +9834,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8667</t>
+          <t>8636</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>16212</t>
+          <t>16389</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9869,12 +9869,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8587</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>15892</t>
+          <t>15612</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>19598</t>
+          <t>19915</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>30652</t>
+          <t>29971</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>73,52%</t>
         </is>
       </c>
     </row>
@@ -9947,12 +9947,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2968</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10541</t>
+          <t>10700</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9982,12 +9982,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4265</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11570</t>
+          <t>11910</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>9017</t>
+          <t>9330</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>19800</t>
+          <t>19617</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,12%</t>
         </is>
       </c>
     </row>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4960</t>
+          <t>5158</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10080,7 +10080,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10135,7 +10135,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4917</t>
+          <t>5579</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -10516,12 +10516,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6558</t>
+          <t>6414</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>15222</t>
+          <t>15195</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10531,12 +10531,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>7997</t>
+          <t>8194</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>16341</t>
+          <t>16530</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>16830</t>
+          <t>16724</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>29146</t>
+          <t>28516</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>54,15%</t>
         </is>
       </c>
     </row>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>10862</t>
+          <t>10978</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>19802</t>
+          <t>20231</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10644,12 +10644,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10664,12 +10664,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>6184</t>
+          <t>5988</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>14702</t>
+          <t>13907</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10699,12 +10699,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>18966</t>
+          <t>19528</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>31509</t>
+          <t>31899</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>60,57%</t>
         </is>
       </c>
     </row>
@@ -10747,7 +10747,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4912</t>
+          <t>4441</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10817,7 +10817,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>5192</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10832,7 +10832,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -10973,7 +10973,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>5122</t>
+          <t>5154</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4333</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11023,7 +11023,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11038,12 +11038,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>732</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6560</t>
+          <t>6622</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11058,7 +11058,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,57%</t>
         </is>
       </c>
     </row>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>19921</t>
+          <t>20462</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>32068</t>
+          <t>32510</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11213,12 +11213,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>62,65%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11233,12 +11233,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>19485</t>
+          <t>19654</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>31271</t>
+          <t>31110</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11268,12 +11268,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>43318</t>
+          <t>44299</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>60458</t>
+          <t>59691</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>57,01%</t>
         </is>
       </c>
     </row>
@@ -11311,12 +11311,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>16219</t>
+          <t>16756</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>28525</t>
+          <t>28741</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11326,12 +11326,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>18499</t>
+          <t>18826</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>30780</t>
+          <t>30015</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>56,84%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11381,12 +11381,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>38168</t>
+          <t>38164</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>54647</t>
+          <t>54253</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11396,12 +11396,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>51,82%</t>
         </is>
       </c>
     </row>
@@ -11424,12 +11424,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>694</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>6776</t>
+          <t>6335</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11439,12 +11439,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11459,12 +11459,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>672</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>5887</t>
+          <t>5765</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11474,12 +11474,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11494,12 +11494,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2510</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>10616</t>
+          <t>9416</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -11542,7 +11542,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3733</t>
+          <t>2745</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11557,7 +11557,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11577,7 +11577,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>3748</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11592,7 +11592,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>4152</t>
+          <t>4509</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -11880,12 +11880,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>19462</t>
+          <t>19449</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>33103</t>
+          <t>33105</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -11915,12 +11915,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>22510</t>
+          <t>23484</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>36639</t>
+          <t>36864</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11930,12 +11930,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11950,12 +11950,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>46673</t>
+          <t>45980</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>66004</t>
+          <t>65368</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11965,12 +11965,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,18%</t>
         </is>
       </c>
     </row>
@@ -11993,12 +11993,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>34410</t>
+          <t>33873</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>48259</t>
+          <t>47749</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12028,12 +12028,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>27515</t>
+          <t>27198</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>40852</t>
+          <t>40403</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12043,12 +12043,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>64987</t>
+          <t>65438</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>86140</t>
+          <t>86214</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12078,12 +12078,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,64%</t>
         </is>
       </c>
     </row>
@@ -12106,12 +12106,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>4721</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>14617</t>
+          <t>13993</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>6650</t>
+          <t>7043</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>16597</t>
+          <t>16507</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>14579</t>
+          <t>13563</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>27732</t>
+          <t>26555</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12191,12 +12191,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,14%</t>
         </is>
       </c>
     </row>
@@ -12224,7 +12224,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>4335</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12259,7 +12259,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12289,12 +12289,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>592</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>5921</t>
+          <t>5376</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12304,12 +12304,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -12337,7 +12337,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>3523</t>
+          <t>3795</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12352,7 +12352,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>4152</t>
+          <t>4448</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -12387,7 +12387,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -12402,12 +12402,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>620</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>5517</t>
+          <t>5984</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -12562,12 +12562,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>146711</t>
+          <t>149445</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>176647</t>
+          <t>179201</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12597,12 +12597,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>165415</t>
+          <t>166109</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>196914</t>
+          <t>194846</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12612,12 +12612,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>323956</t>
+          <t>324900</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>365437</t>
+          <t>366658</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12647,12 +12647,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,86%</t>
         </is>
       </c>
     </row>
@@ -12675,12 +12675,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>101920</t>
+          <t>100128</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>130336</t>
+          <t>127750</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12710,12 +12710,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>98940</t>
+          <t>97458</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>125690</t>
+          <t>126446</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12725,12 +12725,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12745,12 +12745,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>207592</t>
+          <t>207175</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>246931</t>
+          <t>244762</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12760,12 +12760,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,62%</t>
         </is>
       </c>
     </row>
@@ -12788,12 +12788,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>17860</t>
+          <t>17531</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>33817</t>
+          <t>33132</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12823,12 +12823,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>15599</t>
+          <t>15998</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>30668</t>
+          <t>30337</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12838,12 +12838,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12858,12 +12858,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>37379</t>
+          <t>36830</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>58702</t>
+          <t>58757</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -12901,12 +12901,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1239</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>7404</t>
+          <t>7136</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12921,7 +12921,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>8081</t>
+          <t>7714</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12951,12 +12951,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12971,12 +12971,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>3829</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>11571</t>
+          <t>12804</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -13014,12 +13014,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>9845</t>
+          <t>9777</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13029,12 +13029,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13049,12 +13049,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7416</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13064,12 +13064,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13084,12 +13084,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>4099</t>
+          <t>4167</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>13442</t>
+          <t>13854</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13099,12 +13099,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -13285,7 +13285,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido hablar de todos sus amigos en 2016 (tasa de respuesta: 95,28%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as en 2016 (tasa de respuesta: 95,28%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14131</t>
+          <t>14261</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22003</t>
+          <t>21977</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13495,12 +13495,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13515,12 +13515,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9365</t>
+          <t>9242</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18070</t>
+          <t>17984</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13530,12 +13530,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13550,12 +13550,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26856</t>
+          <t>27031</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38377</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13565,12 +13565,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>73,66%</t>
         </is>
       </c>
     </row>
@@ -13593,12 +13593,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3011</t>
+          <t>2876</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10229</t>
+          <t>9936</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13608,12 +13608,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13628,12 +13628,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3894</t>
+          <t>3837</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11519</t>
+          <t>11876</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13663,12 +13663,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8662</t>
+          <t>8416</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19101</t>
+          <t>18720</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13678,12 +13678,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>35,88%</t>
         </is>
       </c>
     </row>
@@ -13706,12 +13706,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>535</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5344</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13721,12 +13721,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13741,12 +13741,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>721</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7085</t>
+          <t>6879</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13756,12 +13756,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2378</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10113</t>
+          <t>9339</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>17,9%</t>
         </is>
       </c>
     </row>
@@ -13859,7 +13859,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3297</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13909,7 +13909,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -13972,7 +13972,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3624</t>
+          <t>2612</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -13987,7 +13987,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2871</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14022,7 +14022,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -14162,12 +14162,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25593</t>
+          <t>25655</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37417</t>
+          <t>37653</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14177,12 +14177,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14197,12 +14197,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33631</t>
+          <t>33857</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44597</t>
+          <t>45287</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14212,12 +14212,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14232,12 +14232,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62814</t>
+          <t>63099</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79827</t>
+          <t>79877</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14247,12 +14247,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,48%</t>
         </is>
       </c>
     </row>
@@ -14275,12 +14275,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14001</t>
+          <t>13292</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25803</t>
+          <t>25561</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14290,12 +14290,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14310,12 +14310,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9197</t>
+          <t>9082</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19857</t>
+          <t>19572</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14325,12 +14325,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14345,12 +14345,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25843</t>
+          <t>25529</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>42469</t>
+          <t>41513</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14360,12 +14360,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>38,19%</t>
         </is>
       </c>
     </row>
@@ -14393,7 +14393,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4543</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14408,7 +14408,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14428,7 +14428,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5778</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14443,7 +14443,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>720</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7391</t>
+          <t>7265</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14478,7 +14478,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -14541,7 +14541,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3638</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14556,7 +14556,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14576,7 +14576,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3419</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17616</t>
+          <t>17360</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27706</t>
+          <t>27383</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -14859,12 +14859,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14879,12 +14879,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19020</t>
+          <t>19281</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27884</t>
+          <t>27820</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -14894,12 +14894,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14914,12 +14914,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40241</t>
+          <t>39886</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53491</t>
+          <t>53185</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -14929,12 +14929,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,27%</t>
         </is>
       </c>
     </row>
@@ -14957,12 +14957,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6703</t>
+          <t>7063</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16379</t>
+          <t>17478</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -14972,12 +14972,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14992,12 +14992,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1531</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8291</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15007,12 +15007,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15027,12 +15027,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9861</t>
+          <t>10096</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21879</t>
+          <t>21566</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15042,12 +15042,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,33%</t>
         </is>
       </c>
     </row>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>5404</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15105,12 +15105,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2157</t>
+          <t>2202</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8824</t>
+          <t>9373</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15120,12 +15120,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15140,12 +15140,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2950</t>
+          <t>3605</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11454</t>
+          <t>12001</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15155,12 +15155,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>17,44%</t>
         </is>
       </c>
     </row>
@@ -15526,12 +15526,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19011</t>
+          <t>19042</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27549</t>
+          <t>27631</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15541,12 +15541,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15561,12 +15561,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22836</t>
+          <t>22321</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32007</t>
+          <t>31868</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15576,12 +15576,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15596,12 +15596,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>44670</t>
+          <t>44606</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>57597</t>
+          <t>57142</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15611,12 +15611,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>82,32%</t>
         </is>
       </c>
     </row>
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1786</t>
+          <t>1711</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7868</t>
+          <t>7545</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15654,12 +15654,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -15674,12 +15674,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3291</t>
+          <t>3525</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11647</t>
+          <t>11974</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15689,12 +15689,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -15709,12 +15709,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6255</t>
+          <t>6436</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>16064</t>
+          <t>16261</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15724,12 +15724,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,43%</t>
         </is>
       </c>
     </row>
@@ -15752,12 +15752,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8681</t>
+          <t>8865</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15767,12 +15767,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4523</t>
+          <t>4587</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15822,12 +15822,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2163</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10675</t>
+          <t>11277</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15837,12 +15837,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>16,25%</t>
         </is>
       </c>
     </row>
@@ -15983,7 +15983,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -15998,7 +15998,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16018,7 +16018,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3226</t>
+          <t>2905</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16053,7 +16053,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>4632</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16068,7 +16068,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -16208,12 +16208,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3843</t>
+          <t>4010</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11308</t>
+          <t>11112</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16223,12 +16223,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16243,12 +16243,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>2657</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9839</t>
+          <t>9912</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16258,12 +16258,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16278,12 +16278,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>8662</t>
+          <t>8078</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>18811</t>
+          <t>18124</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16293,12 +16293,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>40,56%</t>
         </is>
       </c>
     </row>
@@ -16321,12 +16321,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4943</t>
+          <t>4858</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12330</t>
+          <t>12258</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16336,12 +16336,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>11953</t>
+          <t>11344</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>20112</t>
+          <t>19781</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16371,12 +16371,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16391,12 +16391,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>19459</t>
+          <t>18876</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>30227</t>
+          <t>29892</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16406,12 +16406,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>66,9%</t>
         </is>
       </c>
     </row>
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6794</t>
+          <t>6750</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16449,12 +16449,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16469,12 +16469,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>627</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5717</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16484,12 +16484,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2992</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>10033</t>
+          <t>9961</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16519,12 +16519,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,29%</t>
         </is>
       </c>
     </row>
@@ -16587,7 +16587,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>3810</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -16602,7 +16602,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -16622,7 +16622,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4165</t>
+          <t>4109</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -16637,7 +16637,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -16700,7 +16700,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3396</t>
+          <t>2788</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16715,7 +16715,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -16735,7 +16735,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2985</t>
+          <t>3712</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -16750,7 +16750,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -16890,12 +16890,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>15323</t>
+          <t>15213</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>24209</t>
+          <t>23806</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16905,12 +16905,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16925,12 +16925,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>16634</t>
+          <t>17437</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>25794</t>
+          <t>25871</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -16940,12 +16940,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>35416</t>
+          <t>34741</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>47657</t>
+          <t>47815</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16975,12 +16975,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,69%</t>
         </is>
       </c>
     </row>
@@ -17003,12 +17003,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>4359</t>
+          <t>5090</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13044</t>
+          <t>13150</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -17018,12 +17018,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -17038,12 +17038,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>11858</t>
+          <t>11352</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17053,12 +17053,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>10464</t>
+          <t>10115</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>22114</t>
+          <t>21262</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17088,12 +17088,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>34,99%</t>
         </is>
       </c>
     </row>
@@ -17121,7 +17121,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5229</t>
+          <t>5657</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17136,7 +17136,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17156,7 +17156,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5095</t>
+          <t>3782</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>631</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6854</t>
+          <t>6614</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17201,12 +17201,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -17269,7 +17269,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17284,7 +17284,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3485</t>
+          <t>4492</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -17572,12 +17572,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>33292</t>
+          <t>33978</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>47205</t>
+          <t>47322</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -17587,12 +17587,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -17607,12 +17607,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>31272</t>
+          <t>31236</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>44509</t>
+          <t>44174</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -17622,12 +17622,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>69437</t>
+          <t>69174</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>88220</t>
+          <t>87937</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -17657,12 +17657,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,17%</t>
         </is>
       </c>
     </row>
@@ -17685,12 +17685,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>11704</t>
+          <t>12093</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>23852</t>
+          <t>24462</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -17700,12 +17700,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -17720,12 +17720,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>11563</t>
+          <t>11955</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>23711</t>
+          <t>23829</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -17735,12 +17735,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -17755,12 +17755,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>27205</t>
+          <t>26882</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>43523</t>
+          <t>43638</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -17770,12 +17770,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,33%</t>
         </is>
       </c>
     </row>
@@ -17798,12 +17798,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>4138</t>
+          <t>4143</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>13529</t>
+          <t>12869</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -17818,7 +17818,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -17833,12 +17833,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>3364</t>
+          <t>3149</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>11538</t>
+          <t>11049</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -17848,12 +17848,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -17868,12 +17868,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>9495</t>
+          <t>8581</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>21364</t>
+          <t>20715</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -17883,12 +17883,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>15,82%</t>
         </is>
       </c>
     </row>
@@ -17916,7 +17916,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>4505</t>
+          <t>4445</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -17931,7 +17931,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -17951,7 +17951,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>4075</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -17966,7 +17966,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -17981,12 +17981,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>686</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>5885</t>
+          <t>6067</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -18001,7 +18001,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -18029,7 +18029,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3149</t>
+          <t>2893</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -18044,7 +18044,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -18099,7 +18099,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>3170</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -18114,7 +18114,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -18254,12 +18254,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>31604</t>
+          <t>32362</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>46101</t>
+          <t>46219</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -18269,12 +18269,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -18289,12 +18289,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>28570</t>
+          <t>29383</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>42943</t>
+          <t>44147</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -18304,12 +18304,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -18324,12 +18324,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>64371</t>
+          <t>65937</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>84657</t>
+          <t>86113</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -18339,12 +18339,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>55,12%</t>
         </is>
       </c>
     </row>
@@ -18367,12 +18367,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>24628</t>
+          <t>24162</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>38295</t>
+          <t>38158</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -18382,12 +18382,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -18402,12 +18402,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>25509</t>
+          <t>25305</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>39717</t>
+          <t>39974</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -18417,12 +18417,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -18437,12 +18437,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>53654</t>
+          <t>54395</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>72951</t>
+          <t>73169</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -18452,12 +18452,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>46,84%</t>
         </is>
       </c>
     </row>
@@ -18480,12 +18480,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>4098</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>12854</t>
+          <t>12840</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -18495,12 +18495,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -18515,12 +18515,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3321</t>
+          <t>2860</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>11958</t>
+          <t>11381</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -18530,12 +18530,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -18550,12 +18550,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>8990</t>
+          <t>8823</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>21406</t>
+          <t>21476</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -18565,12 +18565,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -18593,12 +18593,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>562</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>5566</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -18613,7 +18613,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -18663,12 +18663,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>558</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>6359</t>
+          <t>5339</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -18683,7 +18683,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>3066</t>
+          <t>3091</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -18726,7 +18726,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -18746,7 +18746,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>3569</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -18761,7 +18761,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -18781,7 +18781,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>4073</t>
+          <t>4083</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -18936,12 +18936,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>188591</t>
+          <t>188942</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>219781</t>
+          <t>219907</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -18951,12 +18951,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -18971,12 +18971,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>192969</t>
+          <t>192035</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>221476</t>
+          <t>221772</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -18986,12 +18986,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -19006,12 +19006,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>389288</t>
+          <t>390803</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>434426</t>
+          <t>434316</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -19021,12 +19021,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>62,79%</t>
         </is>
       </c>
     </row>
@@ -19049,12 +19049,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>93190</t>
+          <t>91155</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>121084</t>
+          <t>121751</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -19064,12 +19064,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>90945</t>
+          <t>91284</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>119181</t>
+          <t>120261</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -19099,12 +19099,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -19119,12 +19119,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>190006</t>
+          <t>191305</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>230938</t>
+          <t>231753</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,5%</t>
         </is>
       </c>
     </row>
@@ -19162,12 +19162,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>21476</t>
+          <t>21560</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>38627</t>
+          <t>38650</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -19177,12 +19177,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>20878</t>
+          <t>20120</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>38106</t>
+          <t>36633</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -19212,12 +19212,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -19232,12 +19232,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>45268</t>
+          <t>46098</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>70496</t>
+          <t>70166</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -19247,12 +19247,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>8028</t>
+          <t>8043</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -19310,12 +19310,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>8134</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -19325,12 +19325,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -19345,12 +19345,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>3697</t>
+          <t>3598</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>13464</t>
+          <t>13324</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -19360,12 +19360,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -19393,7 +19393,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>5517</t>
+          <t>5620</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -19408,7 +19408,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -19423,12 +19423,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>639</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -19438,12 +19438,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -19458,12 +19458,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>10021</t>
+          <t>9521</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -19473,12 +19473,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
